--- a/2b0ba7d73c6d/KZH5-grafik-2026-09-24.xlsx
+++ b/2b0ba7d73c6d/KZH5-grafik-2026-09-24.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Помощь" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlfn_AGGREGATE" hidden="0" function="0" vbProcedure="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'График по датам'!$B$1:$BE$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'График по датам'!$B$1:$BF$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -34,7 +34,7 @@
     <numFmt numFmtId="172" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* \-??[$€-1]_-"/>
     <numFmt numFmtId="173" formatCode="#,##0&quot; Kз&quot;;\-#,##0&quot; Kз&quot;"/>
     <numFmt numFmtId="174" formatCode="_-* #,##0.00_т_._-;\-* #,##0.00_т_._-;_-* \-??_т_._-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="d"/>
+    <numFmt numFmtId="175" formatCode="[$-419]mmm\.yy;@"/>
     <numFmt numFmtId="176" formatCode="0;-0;;@"/>
   </numFmts>
   <fonts count="21">
@@ -746,13 +746,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -769,9 +772,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1528,13 +1528,13 @@
     <col width="11.7" customWidth="1" style="95" min="12" max="12"/>
     <col width="6.85" customWidth="1" style="95" min="13" max="13"/>
     <col width="11.28" customWidth="1" style="95" min="14" max="14"/>
-    <col width="2.85" customWidth="1" style="95" min="15" max="42"/>
-    <col width="2.85" customWidth="1" style="73" min="43" max="59"/>
-    <col hidden="1" width="2.85" customWidth="1" style="73" min="60" max="73"/>
-    <col hidden="1" width="3.85" customWidth="1" style="73" min="74" max="74"/>
-    <col hidden="1" width="3.56" customWidth="1" style="73" min="75" max="75"/>
-    <col hidden="1" width="3.99" customWidth="1" style="73" min="76" max="76"/>
-    <col hidden="1" width="2.85" customWidth="1" style="73" min="77" max="79"/>
+    <col width="4" customWidth="1" style="95" min="15" max="42"/>
+    <col width="4" customWidth="1" style="73" min="43" max="59"/>
+    <col hidden="1" width="4" customWidth="1" style="73" min="60" max="73"/>
+    <col hidden="1" width="4" customWidth="1" style="73" min="74" max="74"/>
+    <col hidden="1" width="4" customWidth="1" style="73" min="75" max="75"/>
+    <col hidden="1" width="4" customWidth="1" style="73" min="76" max="76"/>
+    <col hidden="1" width="4" customWidth="1" style="73" min="77" max="79"/>
     <col hidden="1" width="2.42" customWidth="1" style="73" min="80" max="80"/>
     <col hidden="1" width="2.28" customWidth="1" style="73" min="81" max="81"/>
     <col hidden="1" width="3.28" customWidth="1" style="73" min="82" max="82"/>
@@ -1772,49 +1772,49 @@
       <c r="AV3" s="86" t="n"/>
       <c r="AW3" s="86" t="n"/>
       <c r="AX3" s="87" t="n"/>
-      <c r="AY3" s="88">
+      <c r="AY3" s="105">
         <f>(AY5+AZ5+BA5+BB5)/4</f>
         <v/>
       </c>
       <c r="AZ3" s="86" t="n"/>
       <c r="BA3" s="86" t="n"/>
       <c r="BB3" s="87" t="n"/>
-      <c r="BC3" s="88">
+      <c r="BC3" s="105">
         <f>(BC5+BD5+BE5+BF5)/4</f>
         <v/>
       </c>
       <c r="BD3" s="86" t="n"/>
       <c r="BE3" s="86" t="n"/>
       <c r="BF3" s="87" t="n"/>
-      <c r="BG3" s="88">
+      <c r="BG3" s="105">
         <f>(BG5+BH5+BI5+BJ5)/4</f>
         <v/>
       </c>
       <c r="BH3" s="86" t="n"/>
       <c r="BI3" s="86" t="n"/>
       <c r="BJ3" s="87" t="n"/>
-      <c r="BK3" s="88">
+      <c r="BK3" s="105">
         <f>(BK5+BL5+BM5+BN5)/4</f>
         <v/>
       </c>
       <c r="BL3" s="86" t="n"/>
       <c r="BM3" s="86" t="n"/>
       <c r="BN3" s="87" t="n"/>
-      <c r="BO3" s="88">
+      <c r="BO3" s="105">
         <f>(BO5+BP5+BQ5+BR5)/4</f>
         <v/>
       </c>
       <c r="BP3" s="86" t="n"/>
       <c r="BQ3" s="86" t="n"/>
       <c r="BR3" s="87" t="n"/>
-      <c r="BS3" s="88">
+      <c r="BS3" s="105">
         <f>(BS5+BT5+BU5+BV5)/4</f>
         <v/>
       </c>
       <c r="BT3" s="86" t="n"/>
       <c r="BU3" s="86" t="n"/>
       <c r="BV3" s="87" t="n"/>
-      <c r="BW3" s="88">
+      <c r="BW3" s="105">
         <f>(BW5+BX5+BY5+BZ5)/4</f>
         <v/>
       </c>
@@ -1874,147 +1874,147 @@
           <t>Оконч.</t>
         </is>
       </c>
-      <c r="O4" s="105">
+      <c r="O4" s="106">
         <f>LOOKUP(WEEKDAY(O5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="P4" s="105">
+      <c r="P4" s="106">
         <f>LOOKUP(WEEKDAY(P5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="Q4" s="105">
+      <c r="Q4" s="106">
         <f>LOOKUP(WEEKDAY(Q5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="R4" s="105">
+      <c r="R4" s="106">
         <f>LOOKUP(WEEKDAY(R5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="S4" s="105">
+      <c r="S4" s="106">
         <f>LOOKUP(WEEKDAY(S5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="T4" s="105">
+      <c r="T4" s="106">
         <f>LOOKUP(WEEKDAY(T5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="U4" s="105">
+      <c r="U4" s="106">
         <f>LOOKUP(WEEKDAY(U5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="V4" s="105">
+      <c r="V4" s="106">
         <f>LOOKUP(WEEKDAY(V5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="W4" s="105">
+      <c r="W4" s="106">
         <f>LOOKUP(WEEKDAY(W5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="X4" s="105">
+      <c r="X4" s="106">
         <f>LOOKUP(WEEKDAY(X5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="Y4" s="105">
+      <c r="Y4" s="106">
         <f>LOOKUP(WEEKDAY(Y5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="Z4" s="105">
+      <c r="Z4" s="106">
         <f>LOOKUP(WEEKDAY(Z5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AA4" s="105">
+      <c r="AA4" s="106">
         <f>LOOKUP(WEEKDAY(AA5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AB4" s="105">
+      <c r="AB4" s="106">
         <f>LOOKUP(WEEKDAY(AB5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AC4" s="105">
+      <c r="AC4" s="106">
         <f>LOOKUP(WEEKDAY(AC5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AD4" s="105">
+      <c r="AD4" s="106">
         <f>LOOKUP(WEEKDAY(AD5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AE4" s="105">
+      <c r="AE4" s="106">
         <f>LOOKUP(WEEKDAY(AE5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AF4" s="105">
+      <c r="AF4" s="106">
         <f>LOOKUP(WEEKDAY(AF5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AG4" s="105">
+      <c r="AG4" s="106">
         <f>LOOKUP(WEEKDAY(AG5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AH4" s="105">
+      <c r="AH4" s="106">
         <f>LOOKUP(WEEKDAY(AH5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AI4" s="105">
+      <c r="AI4" s="106">
         <f>LOOKUP(WEEKDAY(AI5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AJ4" s="105">
+      <c r="AJ4" s="106">
         <f>LOOKUP(WEEKDAY(AJ5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AK4" s="105">
+      <c r="AK4" s="106">
         <f>LOOKUP(WEEKDAY(AK5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AL4" s="105">
+      <c r="AL4" s="106">
         <f>LOOKUP(WEEKDAY(AL5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AM4" s="105">
+      <c r="AM4" s="106">
         <f>LOOKUP(WEEKDAY(AM5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AN4" s="105">
+      <c r="AN4" s="106">
         <f>LOOKUP(WEEKDAY(AN5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AO4" s="105">
+      <c r="AO4" s="106">
         <f>LOOKUP(WEEKDAY(AO5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AP4" s="105">
+      <c r="AP4" s="106">
         <f>LOOKUP(WEEKDAY(AP5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AQ4" s="105">
+      <c r="AQ4" s="106">
         <f>LOOKUP(WEEKDAY(AQ5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AR4" s="105">
+      <c r="AR4" s="106">
         <f>LOOKUP(WEEKDAY(AR5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AS4" s="105">
+      <c r="AS4" s="106">
         <f>LOOKUP(WEEKDAY(AS5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AT4" s="105">
+      <c r="AT4" s="106">
         <f>LOOKUP(WEEKDAY(AT5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AU4" s="105">
+      <c r="AU4" s="106">
         <f>LOOKUP(WEEKDAY(AU5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AV4" s="105">
+      <c r="AV4" s="106">
         <f>LOOKUP(WEEKDAY(AV5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AW4" s="105">
+      <c r="AW4" s="106">
         <f>LOOKUP(WEEKDAY(AW5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AX4" s="105">
+      <c r="AX4" s="106">
         <f>LOOKUP(WEEKDAY(AX5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
@@ -2151,196 +2151,196 @@
       <c r="L5" s="91" t="n"/>
       <c r="M5" s="91" t="n"/>
       <c r="N5" s="91" t="n"/>
-      <c r="O5" s="106" t="n">
+      <c r="O5" s="107" t="n">
         <v>46266</v>
       </c>
-      <c r="P5" s="106" t="n">
+      <c r="P5" s="107" t="n">
         <v>46267</v>
       </c>
-      <c r="Q5" s="106" t="n">
+      <c r="Q5" s="107" t="n">
         <v>46268</v>
       </c>
-      <c r="R5" s="106" t="n">
+      <c r="R5" s="107" t="n">
         <v>46269</v>
       </c>
-      <c r="S5" s="106" t="n">
+      <c r="S5" s="107" t="n">
         <v>46270</v>
       </c>
-      <c r="T5" s="106" t="n">
+      <c r="T5" s="107" t="n">
         <v>46271</v>
       </c>
-      <c r="U5" s="106" t="n">
+      <c r="U5" s="107" t="n">
         <v>46272</v>
       </c>
-      <c r="V5" s="106" t="n">
+      <c r="V5" s="107" t="n">
         <v>46273</v>
       </c>
-      <c r="W5" s="106" t="n">
+      <c r="W5" s="107" t="n">
         <v>46274</v>
       </c>
-      <c r="X5" s="106" t="n">
+      <c r="X5" s="107" t="n">
         <v>46275</v>
       </c>
-      <c r="Y5" s="106" t="n">
+      <c r="Y5" s="107" t="n">
         <v>46276</v>
       </c>
-      <c r="Z5" s="106" t="n">
+      <c r="Z5" s="107" t="n">
         <v>46277</v>
       </c>
-      <c r="AA5" s="106" t="n">
+      <c r="AA5" s="107" t="n">
         <v>46278</v>
       </c>
-      <c r="AB5" s="106" t="n">
+      <c r="AB5" s="107" t="n">
         <v>46279</v>
       </c>
-      <c r="AC5" s="106" t="n">
+      <c r="AC5" s="107" t="n">
         <v>46280</v>
       </c>
-      <c r="AD5" s="106" t="n">
+      <c r="AD5" s="107" t="n">
         <v>46281</v>
       </c>
-      <c r="AE5" s="106" t="n">
+      <c r="AE5" s="107" t="n">
         <v>46282</v>
       </c>
-      <c r="AF5" s="106" t="n">
+      <c r="AF5" s="107" t="n">
         <v>46283</v>
       </c>
-      <c r="AG5" s="106" t="n">
+      <c r="AG5" s="107" t="n">
         <v>46284</v>
       </c>
-      <c r="AH5" s="106" t="n">
+      <c r="AH5" s="107" t="n">
         <v>46285</v>
       </c>
-      <c r="AI5" s="106" t="n">
+      <c r="AI5" s="107" t="n">
         <v>46286</v>
       </c>
-      <c r="AJ5" s="106" t="n">
+      <c r="AJ5" s="107" t="n">
         <v>46287</v>
       </c>
-      <c r="AK5" s="106" t="n">
+      <c r="AK5" s="107" t="n">
         <v>46288</v>
       </c>
-      <c r="AL5" s="106" t="n">
+      <c r="AL5" s="107" t="n">
         <v>46289</v>
       </c>
-      <c r="AM5" s="106" t="n">
+      <c r="AM5" s="107" t="n">
         <v>46290</v>
       </c>
-      <c r="AN5" s="106" t="n">
+      <c r="AN5" s="107" t="n">
         <v>46291</v>
       </c>
-      <c r="AO5" s="106" t="n">
+      <c r="AO5" s="107" t="n">
         <v>46292</v>
       </c>
-      <c r="AP5" s="106" t="n">
+      <c r="AP5" s="107" t="n">
         <v>46293</v>
       </c>
-      <c r="AQ5" s="106" t="n">
+      <c r="AQ5" s="107" t="n">
         <v>46294</v>
       </c>
-      <c r="AR5" s="106" t="n">
+      <c r="AR5" s="107" t="n">
         <v>46295</v>
       </c>
-      <c r="AS5" s="106" t="n">
+      <c r="AS5" s="107" t="n">
         <v>46296</v>
       </c>
-      <c r="AT5" s="106" t="n">
+      <c r="AT5" s="107" t="n">
         <v>46297</v>
       </c>
-      <c r="AU5" s="106" t="n">
+      <c r="AU5" s="107" t="n">
         <v>46298</v>
       </c>
-      <c r="AV5" s="106" t="n">
+      <c r="AV5" s="107" t="n">
         <v>46299</v>
       </c>
-      <c r="AW5" s="106" t="n">
+      <c r="AW5" s="107" t="n">
         <v>46300</v>
       </c>
-      <c r="AX5" s="106" t="n">
+      <c r="AX5" s="107" t="n">
         <v>46301</v>
       </c>
-      <c r="AY5" s="106" t="n">
+      <c r="AY5" s="107" t="n">
         <v>46302</v>
       </c>
-      <c r="AZ5" s="106" t="n">
+      <c r="AZ5" s="107" t="n">
         <v>46303</v>
       </c>
-      <c r="BA5" s="106" t="n">
+      <c r="BA5" s="107" t="n">
         <v>46304</v>
       </c>
-      <c r="BB5" s="106" t="n">
+      <c r="BB5" s="107" t="n">
         <v>46305</v>
       </c>
-      <c r="BC5" s="106" t="n">
+      <c r="BC5" s="107" t="n">
         <v>46306</v>
       </c>
-      <c r="BD5" s="106" t="n">
+      <c r="BD5" s="107" t="n">
         <v>46307</v>
       </c>
-      <c r="BE5" s="106" t="n">
+      <c r="BE5" s="107" t="n">
         <v>46308</v>
       </c>
-      <c r="BF5" s="106" t="n">
+      <c r="BF5" s="107" t="n">
         <v>46309</v>
       </c>
-      <c r="BG5" s="106" t="n">
+      <c r="BG5" s="107" t="n">
         <v>46310</v>
       </c>
-      <c r="BH5" s="106" t="n">
+      <c r="BH5" s="107" t="n">
         <v>46311</v>
       </c>
-      <c r="BI5" s="106" t="n">
+      <c r="BI5" s="107" t="n">
         <v>46312</v>
       </c>
-      <c r="BJ5" s="106" t="n">
+      <c r="BJ5" s="107" t="n">
         <v>46313</v>
       </c>
-      <c r="BK5" s="106" t="n">
+      <c r="BK5" s="107" t="n">
         <v>46314</v>
       </c>
-      <c r="BL5" s="106" t="n">
+      <c r="BL5" s="107" t="n">
         <v>46315</v>
       </c>
-      <c r="BM5" s="106" t="n">
+      <c r="BM5" s="107" t="n">
         <v>46316</v>
       </c>
-      <c r="BN5" s="106" t="n">
+      <c r="BN5" s="107" t="n">
         <v>46317</v>
       </c>
-      <c r="BO5" s="106" t="n">
+      <c r="BO5" s="107" t="n">
         <v>46318</v>
       </c>
-      <c r="BP5" s="106" t="n">
+      <c r="BP5" s="107" t="n">
         <v>46319</v>
       </c>
-      <c r="BQ5" s="106" t="n">
+      <c r="BQ5" s="107" t="n">
         <v>46320</v>
       </c>
-      <c r="BR5" s="106" t="n">
+      <c r="BR5" s="107" t="n">
         <v>46321</v>
       </c>
-      <c r="BS5" s="106" t="n">
+      <c r="BS5" s="107" t="n">
         <v>46322</v>
       </c>
-      <c r="BT5" s="106" t="n">
+      <c r="BT5" s="107" t="n">
         <v>46323</v>
       </c>
-      <c r="BU5" s="106" t="n">
+      <c r="BU5" s="107" t="n">
         <v>46324</v>
       </c>
-      <c r="BV5" s="106" t="n">
+      <c r="BV5" s="107" t="n">
         <v>46325</v>
       </c>
-      <c r="BW5" s="106" t="n">
+      <c r="BW5" s="107" t="n">
         <v>46326</v>
       </c>
-      <c r="BX5" s="106" t="n">
+      <c r="BX5" s="107" t="n">
         <v>46327</v>
       </c>
-      <c r="BY5" s="106" t="n">
+      <c r="BY5" s="107" t="n">
         <v>46328</v>
       </c>
-      <c r="BZ5" s="106" t="n">
+      <c r="BZ5" s="107" t="n">
         <v>46329</v>
       </c>
       <c r="CC5" s="73" t="n"/>
@@ -2349,8 +2349,8 @@
     </row>
     <row r="6" hidden="1" s="74">
       <c r="A6" s="102" t="n"/>
-      <c r="B6" s="105" t="n"/>
-      <c r="C6" s="107" t="n"/>
+      <c r="B6" s="106" t="n"/>
+      <c r="C6" s="108" t="n"/>
       <c r="D6" s="102" t="n"/>
       <c r="E6" s="102" t="n"/>
       <c r="F6" s="102" t="n"/>
@@ -2359,53 +2359,53 @@
       <c r="I6" s="102" t="n"/>
       <c r="J6" s="102" t="n"/>
       <c r="K6" s="103" t="n"/>
-      <c r="L6" s="108" t="n"/>
-      <c r="M6" s="105" t="n"/>
-      <c r="N6" s="108" t="n"/>
-      <c r="O6" s="109" t="n"/>
-      <c r="P6" s="109" t="n"/>
-      <c r="Q6" s="109" t="n"/>
-      <c r="R6" s="109" t="n"/>
-      <c r="S6" s="109" t="n"/>
-      <c r="T6" s="109" t="n"/>
-      <c r="U6" s="109" t="n"/>
-      <c r="V6" s="109" t="n"/>
-      <c r="W6" s="109" t="n"/>
-      <c r="X6" s="109" t="n"/>
-      <c r="Y6" s="109" t="n"/>
-      <c r="Z6" s="109" t="n"/>
-      <c r="AA6" s="109" t="n"/>
-      <c r="AB6" s="109" t="n"/>
-      <c r="AC6" s="109" t="n"/>
-      <c r="AD6" s="109" t="n"/>
-      <c r="AE6" s="109" t="n"/>
-      <c r="AF6" s="109" t="n"/>
-      <c r="AG6" s="109" t="n"/>
-      <c r="AH6" s="109" t="n"/>
-      <c r="AI6" s="109" t="n"/>
-      <c r="AJ6" s="109" t="n"/>
-      <c r="AK6" s="109" t="n"/>
-      <c r="AL6" s="109" t="n"/>
-      <c r="AM6" s="109" t="n"/>
-      <c r="AN6" s="109" t="n"/>
-      <c r="AO6" s="109" t="n"/>
-      <c r="AP6" s="109" t="n"/>
-      <c r="AQ6" s="109" t="n"/>
-      <c r="AR6" s="109" t="n"/>
-      <c r="AS6" s="109" t="n"/>
-      <c r="AT6" s="109" t="n"/>
-      <c r="AU6" s="109" t="n"/>
-      <c r="AV6" s="110" t="n"/>
-      <c r="AW6" s="110" t="n"/>
-      <c r="AX6" s="110" t="n"/>
-      <c r="AY6" s="111" t="n"/>
-      <c r="AZ6" s="111" t="n"/>
-      <c r="BA6" s="111" t="n"/>
-      <c r="BB6" s="111" t="n"/>
-      <c r="BC6" s="111" t="n"/>
-      <c r="BD6" s="111" t="n"/>
-      <c r="BE6" s="111" t="n"/>
-      <c r="BF6" s="111" t="n"/>
+      <c r="L6" s="109" t="n"/>
+      <c r="M6" s="106" t="n"/>
+      <c r="N6" s="109" t="n"/>
+      <c r="O6" s="110" t="n"/>
+      <c r="P6" s="110" t="n"/>
+      <c r="Q6" s="110" t="n"/>
+      <c r="R6" s="110" t="n"/>
+      <c r="S6" s="110" t="n"/>
+      <c r="T6" s="110" t="n"/>
+      <c r="U6" s="110" t="n"/>
+      <c r="V6" s="110" t="n"/>
+      <c r="W6" s="110" t="n"/>
+      <c r="X6" s="110" t="n"/>
+      <c r="Y6" s="110" t="n"/>
+      <c r="Z6" s="110" t="n"/>
+      <c r="AA6" s="110" t="n"/>
+      <c r="AB6" s="110" t="n"/>
+      <c r="AC6" s="110" t="n"/>
+      <c r="AD6" s="110" t="n"/>
+      <c r="AE6" s="110" t="n"/>
+      <c r="AF6" s="110" t="n"/>
+      <c r="AG6" s="110" t="n"/>
+      <c r="AH6" s="110" t="n"/>
+      <c r="AI6" s="110" t="n"/>
+      <c r="AJ6" s="110" t="n"/>
+      <c r="AK6" s="110" t="n"/>
+      <c r="AL6" s="110" t="n"/>
+      <c r="AM6" s="110" t="n"/>
+      <c r="AN6" s="110" t="n"/>
+      <c r="AO6" s="110" t="n"/>
+      <c r="AP6" s="110" t="n"/>
+      <c r="AQ6" s="110" t="n"/>
+      <c r="AR6" s="110" t="n"/>
+      <c r="AS6" s="110" t="n"/>
+      <c r="AT6" s="110" t="n"/>
+      <c r="AU6" s="110" t="n"/>
+      <c r="AV6" s="111" t="n"/>
+      <c r="AW6" s="111" t="n"/>
+      <c r="AX6" s="111" t="n"/>
+      <c r="AY6" s="112" t="n"/>
+      <c r="AZ6" s="112" t="n"/>
+      <c r="BA6" s="112" t="n"/>
+      <c r="BB6" s="112" t="n"/>
+      <c r="BC6" s="112" t="n"/>
+      <c r="BD6" s="112" t="n"/>
+      <c r="BE6" s="112" t="n"/>
+      <c r="BF6" s="112" t="n"/>
       <c r="BG6" s="90" t="n"/>
       <c r="BH6" s="90" t="n"/>
       <c r="BI6" s="90" t="n"/>
@@ -2424,18 +2424,18 @@
       <c r="BV6" s="90" t="n"/>
       <c r="BW6" s="90" t="n"/>
       <c r="BX6" s="90" t="n"/>
-      <c r="BY6" s="112" t="n"/>
-      <c r="BZ6" s="112" t="n"/>
+      <c r="BY6" s="107" t="n"/>
+      <c r="BZ6" s="107" t="n"/>
       <c r="CC6" s="73" t="n"/>
       <c r="CD6" s="73" t="n"/>
       <c r="CE6" s="73" t="n"/>
     </row>
     <row r="7" s="74">
       <c r="A7" s="113" t="n"/>
-      <c r="B7" s="105" t="n">
+      <c r="B7" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="107" t="inlineStr">
+      <c r="C7" s="108" t="inlineStr">
         <is>
           <t>Бетонирование КФ РВС№ 13.7</t>
         </is>
@@ -2451,10 +2451,10 @@
       <c r="L7" s="114" t="n">
         <v>46279</v>
       </c>
-      <c r="M7" s="105" t="n">
+      <c r="M7" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="108">
+      <c r="N7" s="109">
         <f>L7+M7-1</f>
         <v/>
       </c>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="8" s="74">
       <c r="A8" s="119" t="n"/>
-      <c r="B8" s="105" t="n">
+      <c r="B8" s="106" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="107" t="inlineStr">
+      <c r="C8" s="108" t="inlineStr">
         <is>
           <t>Бетонирование КФ РВС№ 13.9</t>
         </is>
@@ -2739,7 +2739,7 @@
       <c r="M8" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="N8" s="108">
+      <c r="N8" s="109">
         <f>L8+M8-1</f>
         <v/>
       </c>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="9" s="74">
       <c r="A9" s="113" t="n"/>
-      <c r="B9" s="105" t="n">
+      <c r="B9" s="106" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="107" t="inlineStr">
+      <c r="C9" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС №13.12</t>
         </is>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="10" s="74">
       <c r="A10" s="102" t="n"/>
-      <c r="B10" s="105" t="n">
+      <c r="B10" s="106" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="107" t="inlineStr">
+      <c r="C10" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.11</t>
         </is>
@@ -3303,13 +3303,13 @@
       <c r="I10" s="102" t="n"/>
       <c r="J10" s="102" t="n"/>
       <c r="K10" s="103" t="n"/>
-      <c r="L10" s="108" t="n">
+      <c r="L10" s="109" t="n">
         <v>46281</v>
       </c>
-      <c r="M10" s="105" t="n">
+      <c r="M10" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="109">
         <f>L10+M10-1</f>
         <v/>
       </c>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="11" s="74">
       <c r="A11" s="113" t="n"/>
-      <c r="B11" s="105" t="n">
+      <c r="B11" s="106" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="126" t="inlineStr">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="12" s="74">
       <c r="A12" s="113" t="n"/>
-      <c r="B12" s="105" t="n">
+      <c r="B12" s="106" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="107" t="inlineStr">
+      <c r="C12" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС №13.10</t>
         </is>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="13" s="74">
       <c r="A13" s="119" t="n"/>
-      <c r="B13" s="105" t="n">
+      <c r="B13" s="106" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="107" t="inlineStr">
+      <c r="C13" s="108" t="inlineStr">
         <is>
           <t>Устройство песчаного слоя основания РВС№13.8</t>
         </is>
@@ -4167,7 +4167,7 @@
       <c r="M13" s="122" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="108">
+      <c r="N13" s="109">
         <f>L13+M13-1</f>
         <v/>
       </c>
@@ -4430,10 +4430,10 @@
     </row>
     <row r="14" s="74">
       <c r="A14" s="119" t="n"/>
-      <c r="B14" s="105" t="n">
+      <c r="B14" s="106" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="107" t="inlineStr">
+      <c r="C14" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.8</t>
         </is>
@@ -4452,7 +4452,7 @@
       <c r="M14" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="108">
+      <c r="N14" s="109">
         <f>L14+M14-1</f>
         <v/>
       </c>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="15" s="74">
       <c r="A15" s="119" t="n"/>
-      <c r="B15" s="105" t="n">
+      <c r="B15" s="106" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="126" t="inlineStr">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="16" s="74">
       <c r="A16" s="102" t="n"/>
-      <c r="B16" s="105" t="n">
+      <c r="B16" s="106" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="107" t="inlineStr">
+      <c r="C16" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.6</t>
         </is>
@@ -5038,7 +5038,7 @@
       <c r="M16" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="N16" s="108">
+      <c r="N16" s="109">
         <f>L16+M16-1</f>
         <v/>
       </c>
@@ -5303,10 +5303,10 @@
     </row>
     <row r="17" s="74">
       <c r="A17" s="102" t="n"/>
-      <c r="B17" s="105" t="n">
+      <c r="B17" s="106" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="107" t="inlineStr">
+      <c r="C17" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.5</t>
         </is>
@@ -5325,7 +5325,7 @@
       <c r="M17" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="N17" s="108">
+      <c r="N17" s="109">
         <f>L17+M17-1</f>
         <v/>
       </c>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="18" s="74">
       <c r="A18" s="102" t="n"/>
-      <c r="B18" s="105" t="n">
+      <c r="B18" s="106" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="126" t="inlineStr">
@@ -5789,7 +5789,7 @@
       <c r="M18" s="122" t="n">
         <v>3</v>
       </c>
-      <c r="N18" s="108">
+      <c r="N18" s="109">
         <f>L18+M18-1</f>
         <v/>
       </c>
@@ -6054,10 +6054,10 @@
     </row>
     <row r="19" s="74">
       <c r="A19" s="119" t="n"/>
-      <c r="B19" s="105" t="n">
+      <c r="B19" s="106" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="107" t="inlineStr">
+      <c r="C19" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№ 13.9</t>
         </is>
@@ -6073,7 +6073,7 @@
       <c r="L19" s="131" t="n">
         <v>46292</v>
       </c>
-      <c r="M19" s="105" t="n">
+      <c r="M19" s="106" t="n">
         <v>2</v>
       </c>
       <c r="N19" s="131">
@@ -6347,10 +6347,10 @@
     </row>
     <row r="20" s="74">
       <c r="A20" s="119" t="n"/>
-      <c r="B20" s="105" t="n">
+      <c r="B20" s="106" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="107" t="inlineStr">
+      <c r="C20" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.7</t>
         </is>
@@ -6369,7 +6369,7 @@
       <c r="M20" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="108">
+      <c r="N20" s="109">
         <f>L20+M20-1</f>
         <v/>
       </c>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="21" s="74">
       <c r="A21" s="119" t="n"/>
-      <c r="B21" s="105" t="n">
+      <c r="B21" s="106" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="126" t="inlineStr">
@@ -6933,10 +6933,10 @@
     </row>
     <row r="22" s="74">
       <c r="A22" s="119" t="n"/>
-      <c r="B22" s="105" t="n">
+      <c r="B22" s="106" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="107" t="inlineStr">
+      <c r="C22" s="108" t="inlineStr">
         <is>
           <t>Устройство бетонной подготовки фундаментов КФ  РВС№13.3, 13.4</t>
         </is>
@@ -6952,7 +6952,7 @@
       <c r="L22" s="131" t="n">
         <v>46288</v>
       </c>
-      <c r="M22" s="105" t="n">
+      <c r="M22" s="106" t="n">
         <v>2</v>
       </c>
       <c r="N22" s="131">
@@ -7226,10 +7226,10 @@
     </row>
     <row r="23" s="74">
       <c r="A23" s="119" t="n"/>
-      <c r="B23" s="105" t="n">
+      <c r="B23" s="106" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="107" t="inlineStr">
+      <c r="C23" s="108" t="inlineStr">
         <is>
           <t>Армирование фундаментов РВС№13.3, 13.4</t>
         </is>
@@ -7245,7 +7245,7 @@
       <c r="L23" s="131" t="n">
         <v>46291</v>
       </c>
-      <c r="M23" s="105" t="n">
+      <c r="M23" s="106" t="n">
         <v>2</v>
       </c>
       <c r="N23" s="131">
@@ -7519,10 +7519,10 @@
     </row>
     <row r="24" s="74">
       <c r="A24" s="119" t="n"/>
-      <c r="B24" s="105" t="n">
+      <c r="B24" s="106" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="107" t="inlineStr">
+      <c r="C24" s="108" t="inlineStr">
         <is>
           <t>Бетонирование КФ РВС№13.3, 13.4</t>
         </is>
@@ -7538,7 +7538,7 @@
       <c r="L24" s="131" t="n">
         <v>46295</v>
       </c>
-      <c r="M24" s="105" t="n">
+      <c r="M24" s="106" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="131">
@@ -7812,10 +7812,10 @@
     </row>
     <row r="25" s="74">
       <c r="A25" s="119" t="n"/>
-      <c r="B25" s="105" t="n">
+      <c r="B25" s="106" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="107" t="inlineStr">
+      <c r="C25" s="108" t="inlineStr">
         <is>
           <t>Устройство песчаного слоя основания РВС№13.3, 13.4, 13.9</t>
         </is>
@@ -7831,7 +7831,7 @@
       <c r="L25" s="131" t="n">
         <v>46296</v>
       </c>
-      <c r="M25" s="105" t="n">
+      <c r="M25" s="106" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="131">
@@ -8105,10 +8105,10 @@
     </row>
     <row r="26" s="74">
       <c r="A26" s="119" t="n"/>
-      <c r="B26" s="105" t="n">
+      <c r="B26" s="106" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="107" t="inlineStr">
+      <c r="C26" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.3, 13.4</t>
         </is>
@@ -8124,7 +8124,7 @@
       <c r="L26" s="131" t="n">
         <v>46298</v>
       </c>
-      <c r="M26" s="105" t="n">
+      <c r="M26" s="106" t="n">
         <v>3</v>
       </c>
       <c r="N26" s="131">
@@ -8397,7 +8397,7 @@
       <c r="CH26" s="128" t="n"/>
     </row>
     <row r="27" s="74">
-      <c r="B27" s="105" t="n">
+      <c r="B27" s="106" t="n">
         <v>21</v>
       </c>
       <c r="C27" s="126" t="inlineStr">
@@ -8682,10 +8682,10 @@
     </row>
     <row r="28" s="74">
       <c r="A28" s="119" t="n"/>
-      <c r="B28" s="105" t="n">
+      <c r="B28" s="106" t="n">
         <v>22</v>
       </c>
-      <c r="C28" s="107" t="inlineStr">
+      <c r="C28" s="108" t="inlineStr">
         <is>
           <t>Устройство бетонной подготовки фундаментов КФ  РВС№13.1, 13,2</t>
         </is>
@@ -8701,7 +8701,7 @@
       <c r="L28" s="131" t="n">
         <v>46286</v>
       </c>
-      <c r="M28" s="105" t="n">
+      <c r="M28" s="106" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="131">
@@ -8975,10 +8975,10 @@
     </row>
     <row r="29" s="74">
       <c r="A29" s="119" t="n"/>
-      <c r="B29" s="105" t="n">
+      <c r="B29" s="106" t="n">
         <v>23</v>
       </c>
-      <c r="C29" s="107" t="inlineStr">
+      <c r="C29" s="108" t="inlineStr">
         <is>
           <t>Армирование фундаментов РВС№13.1, 13.2</t>
         </is>
@@ -8994,7 +8994,7 @@
       <c r="L29" s="131" t="n">
         <v>46288</v>
       </c>
-      <c r="M29" s="105" t="n">
+      <c r="M29" s="106" t="n">
         <v>2</v>
       </c>
       <c r="N29" s="131">
@@ -9268,10 +9268,10 @@
     </row>
     <row r="30" s="74">
       <c r="A30" s="119" t="n"/>
-      <c r="B30" s="105" t="n">
+      <c r="B30" s="106" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="107" t="inlineStr">
+      <c r="C30" s="108" t="inlineStr">
         <is>
           <t>Бетонирование КФ РВС№13.1, 13.2</t>
         </is>
@@ -9287,7 +9287,7 @@
       <c r="L30" s="131" t="n">
         <v>46290</v>
       </c>
-      <c r="M30" s="105" t="n">
+      <c r="M30" s="106" t="n">
         <v>2</v>
       </c>
       <c r="N30" s="131">
@@ -9561,10 +9561,10 @@
     </row>
     <row r="31" s="74">
       <c r="A31" s="119" t="n"/>
-      <c r="B31" s="105" t="n">
+      <c r="B31" s="106" t="n">
         <v>25</v>
       </c>
-      <c r="C31" s="107" t="inlineStr">
+      <c r="C31" s="108" t="inlineStr">
         <is>
           <t>Устройство песчаного слоя основания РВС№13.1, 13.2</t>
         </is>
@@ -9580,7 +9580,7 @@
       <c r="L31" s="131" t="n">
         <v>46293</v>
       </c>
-      <c r="M31" s="105" t="n">
+      <c r="M31" s="106" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="131">
@@ -9854,10 +9854,10 @@
     </row>
     <row r="32" s="74">
       <c r="A32" s="119" t="n"/>
-      <c r="B32" s="105" t="n">
+      <c r="B32" s="106" t="n">
         <v>26</v>
       </c>
-      <c r="C32" s="107" t="inlineStr">
+      <c r="C32" s="108" t="inlineStr">
         <is>
           <t>Монтаж геомембраны и устройство защитного слоя  основания РВС№13.1, 13.2</t>
         </is>
@@ -10147,7 +10147,7 @@
     </row>
     <row r="33" s="74">
       <c r="A33" s="119" t="n"/>
-      <c r="B33" s="105" t="n">
+      <c r="B33" s="106" t="n">
         <v>27</v>
       </c>
       <c r="C33" s="126" t="inlineStr">
@@ -10440,7 +10440,7 @@
     </row>
     <row r="34" s="74">
       <c r="A34" s="119" t="n"/>
-      <c r="B34" s="105" t="n">
+      <c r="B34" s="106" t="n">
         <v>28</v>
       </c>
       <c r="C34" s="126" t="inlineStr">
@@ -10733,7 +10733,7 @@
     </row>
     <row r="35" s="74">
       <c r="A35" s="119" t="n"/>
-      <c r="B35" s="105" t="n">
+      <c r="B35" s="106" t="n">
         <v>29</v>
       </c>
       <c r="C35" s="126" t="inlineStr">
@@ -11026,7 +11026,7 @@
     </row>
     <row r="36" s="74">
       <c r="A36" s="119" t="n"/>
-      <c r="B36" s="105" t="n">
+      <c r="B36" s="106" t="n">
         <v>30</v>
       </c>
       <c r="C36" s="126" t="inlineStr">
@@ -11319,7 +11319,7 @@
     </row>
     <row r="37" s="74">
       <c r="A37" s="119" t="n"/>
-      <c r="B37" s="105" t="n">
+      <c r="B37" s="106" t="n">
         <v>31</v>
       </c>
       <c r="C37" s="126" t="inlineStr">
@@ -11612,7 +11612,7 @@
     </row>
     <row r="38" s="74">
       <c r="A38" s="119" t="n"/>
-      <c r="B38" s="105" t="n">
+      <c r="B38" s="106" t="n">
         <v>32</v>
       </c>
       <c r="C38" s="126" t="inlineStr">
@@ -11905,7 +11905,7 @@
     </row>
     <row r="39" s="74">
       <c r="A39" s="113" t="n"/>
-      <c r="B39" s="105" t="n">
+      <c r="B39" s="106" t="n">
         <v>33</v>
       </c>
       <c r="C39" s="126" t="inlineStr">
